--- a/bcmc-vrphd/data/instances/small_n5_k3.xlsx
+++ b/bcmc-vrphd/data/instances/small_n5_k3.xlsx
@@ -459,14 +459,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-Capital</t>
         </is>
       </c>
     </row>
@@ -476,18 +476,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VSP</t>
+          <t>FOB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.2</v>
+        <v>-12.5</v>
       </c>
       <c r="D3" t="n">
-        <v>93.90000000000001</v>
+        <v>-34.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -497,18 +497,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36.2</v>
+        <v>45.1</v>
       </c>
       <c r="D4" t="n">
-        <v>72.3</v>
+        <v>-44.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -518,18 +518,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>FOB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="n">
-        <v>98.3</v>
+        <v>36.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -539,18 +539,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VSP</t>
+          <t>ANP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68.8</v>
+        <v>9.9</v>
       </c>
       <c r="D6" t="n">
-        <v>103.3</v>
+        <v>10.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -560,18 +560,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FOB</t>
+          <t>ANP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37.3</v>
+        <v>-34.4</v>
       </c>
       <c r="D7" t="n">
-        <v>77.3</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -627,21 +627,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HEMTT-A4</t>
+          <t>M978-Tanker</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>122.7</v>
+        <v>184</v>
       </c>
       <c r="D2" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>I,II,IV</t>
+          <t>I,IV,VIII</t>
         </is>
       </c>
     </row>
@@ -651,21 +651,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M978-Tanker</t>
+          <t>HEMTT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>180.3</v>
+        <v>81.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>III-W</t>
+          <t>II,IV,IX</t>
         </is>
       </c>
     </row>
@@ -675,21 +675,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LMTV-M1078</t>
+          <t>M978-Tanker</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.819</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>I,II,VIII,IX</t>
+          <t>III-W,VIII</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="3">
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>46.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>85.5</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="5">
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>99.7</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="6">
@@ -790,158 +790,158 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>53.1</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>58.3</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>14.9</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>21.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>51.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>46.3</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>58.3</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>55.6</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>79.40000000000001</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -950,306 +950,306 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>85.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>14.9</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>55.6</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>27.6</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>47.3</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>99.7</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.3</v>
+        <v>132.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>79.40000000000001</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>27.6</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>72.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>53.1</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>51.4</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>47.3</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>72.09999999999999</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>84.90000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>49.2</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>90.90000000000001</v>
+        <v>119.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>106</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>56.5</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>84.90000000000001</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>61.9</v>
+        <v>129.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
@@ -1258,35 +1258,35 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>15.8</v>
+        <v>132.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>22.7</v>
+        <v>171.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>54.6</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1294,13 +1294,13 @@
         <v>2</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>49.2</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="43">
@@ -1308,13 +1308,13 @@
         <v>2</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>61.9</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="44">
@@ -1322,13 +1322,13 @@
         <v>2</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>59.1</v>
+        <v>197.4</v>
       </c>
     </row>
     <row r="45">
@@ -1336,13 +1336,13 @@
         <v>2</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>84.3</v>
+        <v>193.9</v>
       </c>
     </row>
     <row r="46">
@@ -1353,10 +1353,10 @@
         <v>5</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>9.6</v>
+        <v>184.2</v>
       </c>
     </row>
     <row r="47">
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>90.90000000000001</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="48">
@@ -1378,13 +1378,13 @@
         <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>15.8</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1392,13 +1392,13 @@
         <v>3</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>59.1</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1406,13 +1406,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>29.3</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="51">
@@ -1420,46 +1420,46 @@
         <v>3</v>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>50.3</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>106</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>22.7</v>
+        <v>129.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" t="n">
         <v>2</v>
@@ -1468,306 +1468,306 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>84.3</v>
+        <v>123.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>29.3</v>
+        <v>190.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>76.59999999999999</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>56.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>54.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>9.6</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>50.3</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>76.59999999999999</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>79.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>49.8</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>77.09999999999999</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>97.90000000000001</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>64.59999999999999</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>87.7</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>56.4</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>32.4</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>24.1</v>
+        <v>130.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>49.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>55.7</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>63.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>55</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>83.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B76" t="n">
         <v>5</v>
@@ -1776,147 +1776,147 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>16.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>81.59999999999999</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>23.4</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>68.40000000000001</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>34</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>57.7</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
         <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>104.9</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>32.1</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>88</v>
+        <v>149.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>30.5</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>63.9</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -1924,13 +1924,13 @@
         <v>5</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>55.5</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="88">
@@ -1938,13 +1938,13 @@
         <v>5</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
         <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>48.2</v>
+        <v>133.8</v>
       </c>
     </row>
     <row r="89">
@@ -1952,13 +1952,13 @@
         <v>5</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>17.8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -1966,13 +1966,13 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>58.2</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="91">
@@ -1986,7 +1986,7 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>81.7</v>
+        <v>101.9</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +2000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>III-W</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2039,11 +2039,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>III-W</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4">
@@ -2052,24 +2052,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>VIII</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
@@ -2078,11 +2078,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VIII</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="7">
@@ -2091,11 +2091,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8">
@@ -2104,24 +2104,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>VIII</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>III-W</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>11</v>
+      <c r="C11" t="n">
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -2161,11 +2187,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.71</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="3">
@@ -2174,11 +2200,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.61</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="4">
@@ -2187,11 +2213,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>VIII</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.57</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="5">
@@ -2200,37 +2226,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>III-W</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.970000000000001</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.33</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="8">
@@ -2239,11 +2265,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VIII</t>
+          <t>III-W</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.86</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -2252,11 +2278,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>VIII</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.37</v>
+        <v>4.28</v>
       </c>
     </row>
   </sheetData>
@@ -2290,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>262.2</v>
       </c>
     </row>
     <row r="3">
@@ -2298,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>134.7</v>
+        <v>308.7</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2332,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>133.6</v>
+        <v>363.4</v>
       </c>
     </row>
   </sheetData>
@@ -2341,7 +2367,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-Capital</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2377,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2387,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2397,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2407,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2417,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RC-N</t>
+          <t>RC-S</t>
         </is>
       </c>
     </row>

--- a/bcmc-vrphd/data/instances/small_n5_k3.xlsx
+++ b/bcmc-vrphd/data/instances/small_n5_k3.xlsx
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>VIII</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VIII</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IX</t>
+          <t>II</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>II</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>262.2</v>
+        <v>263.4</v>
       </c>
     </row>
     <row r="3">
@@ -2324,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>308.7</v>
+        <v>308.8</v>
       </c>
     </row>
     <row r="4">
